--- a/tests/data_golden/expansion.expected.xlsx
+++ b/tests/data_golden/expansion.expected.xlsx
@@ -434,19 +434,19 @@
     <t>Sales</t>
   </si>
   <si>
-    <t>No. 1</t>
+    <t xml:space="preserve">No. 1</t>
   </si>
   <si>
     <t>Alice</t>
   </si>
   <si>
-    <t>No. 2</t>
+    <t xml:space="preserve">No. 2</t>
   </si>
   <si>
     <t>Bob</t>
   </si>
   <si>
-    <t>Sales total</t>
+    <t xml:space="preserve">Sales total</t>
   </si>
   <si>
     <t>Dev</t>
@@ -455,7 +455,7 @@
     <t>Carol</t>
   </si>
   <si>
-    <t>Dev total</t>
+    <t xml:space="preserve">Dev total</t>
   </si>
   <si>
     <t>Support</t>
@@ -467,13 +467,13 @@
     <t>Eve</t>
   </si>
   <si>
-    <t>No. 3</t>
+    <t xml:space="preserve">No. 3</t>
   </si>
   <si>
     <t>Frank</t>
   </si>
   <si>
-    <t>Support total</t>
+    <t xml:space="preserve">Support total</t>
   </si>
   <si>
     <t>A</t>
